--- a/coach_roster_template.xlsx
+++ b/coach_roster_template.xlsx
@@ -1931,20 +1931,20 @@
     <mergeCell ref="A7:I7"/>
   </mergeCells>
   <dataValidations count="5">
-    <dataValidation sqref="D8:D107" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Level" prompt="Choose: 0, 0.5, 1.0, 1.5, 2.0, or 2.5" type="list" errorStyle="warning">
-      <formula1>"0,0.5,1.0,1.5,2.0,2.5"</formula1>
+    <dataValidation sqref="D8:D107" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Level" prompt="Choose 0 to 5.0 in 0.5 steps. E.g. 0, 0.5, 1.0, 1.5, 2.0 ..." type="list">
+      <formula1>"0,0.5,1.0,1.5,2.0,2.5,3.0,3.5,4.0,4.5,5.0"</formula1>
     </dataValidation>
-    <dataValidation sqref="F8:F107" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Early Match?" prompt="Yes = wrestler needs an early match." type="list" errorStyle="warning">
-      <formula1>"Yes,No"</formula1>
+    <dataValidation sqref="F8:F107" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Early Match?" prompt="Yes or No (Y and N also accepted)" type="list">
+      <formula1>"Yes,No,Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="G8:G107" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Scratch?" prompt="Yes = not wrestling tonight." type="list" errorStyle="warning">
-      <formula1>"Yes,No"</formula1>
+    <dataValidation sqref="G8:G107" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Scratch?" prompt="Yes or No (Y and N also accepted)" type="list">
+      <formula1>"Yes,No,Y,N"</formula1>
     </dataValidation>
-    <dataValidation sqref="H8:H107" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Gender" prompt="Male or Female. Leave blank if not applicable." type="list" errorStyle="warning">
-      <formula1>"Male,Female"</formula1>
+    <dataValidation sqref="H8:H107" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Gender" prompt="Male or Female (M and F also accepted). Leave blank if not applicable." type="list">
+      <formula1>"Male,Female,M,F"</formula1>
     </dataValidation>
-    <dataValidation sqref="I8:I107" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" promptTitle="Cross Gender OK?" prompt="Yes = can compete vs opposite gender." type="list" errorStyle="warning">
-      <formula1>"Yes,No"</formula1>
+    <dataValidation sqref="I8:I107" showDropDown="0" showInputMessage="1" showErrorMessage="0" allowBlank="1" promptTitle="Cross Gender OK?" prompt="Yes or No (Y and N also accepted). Leave blank if Gender is blank." type="list">
+      <formula1>"Yes,No,Y,N"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
